--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/WYOMING_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/WYOMING_2017.xlsx
@@ -5053,7 +5053,7 @@
         <v>85</v>
       </c>
       <c r="D261">
-        <v>0.09826589595375723</v>
+        <v>0.09826589595375725</v>
       </c>
     </row>
     <row r="262">
